--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R86013b6ffd114cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R6a753e4560a54e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R6079a915b1af4772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R2ef549eec16347ae"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R6079a915b1af4772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R2ef549eec16347ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R16a94d5ce67c4793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Ra7a87c660a7f481b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R16a94d5ce67c4793"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Ra7a87c660a7f481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R27bbc26d81a846dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R6be5e06b2e884098"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R27bbc26d81a846dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R6be5e06b2e884098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R14655d9adf0042f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R829ebab682374d8a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R14655d9adf0042f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R829ebab682374d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rbf15ad5db5544188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc8b0f6cd68244a92"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rbf15ad5db5544188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc8b0f6cd68244a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rcecd15bbef294c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R78ed24edf8334064"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rcecd15bbef294c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R78ed24edf8334064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R398197b8ebf64426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd77ff9ad1a294e9f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R398197b8ebf64426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd77ff9ad1a294e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rfdc06c61e73f4f68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd0adf11ea6c54d6b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rfdc06c61e73f4f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd0adf11ea6c54d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R63726458a21449f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R780aa17ab06b4f15"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R63726458a21449f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R780aa17ab06b4f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rd150809a97d54aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R918be1cb0cfb4471"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rd150809a97d54aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R918be1cb0cfb4471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rb724f0097b3548ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R79529467609f495d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rb724f0097b3548ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R79529467609f495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2ab1f449f9d34520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rcbc22230b8d5499a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2ab1f449f9d34520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rcbc22230b8d5499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R5da53f5ac60c4174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb00938b84c504901"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R5da53f5ac60c4174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb00938b84c504901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Re1db52e2bc50477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rabfe46d7380f4ada"/>
   </x:sheets>
 </x:workbook>
 </file>
